--- a/data/monthly/【2026年1月】月次数値.xlsx
+++ b/data/monthly/【2026年1月】月次数値.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="612" yWindow="600" windowWidth="21792" windowHeight="10812"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="123">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -260,31 +259,159 @@
   </si>
   <si>
     <t>2027-01-12</t>
+  </si>
+  <si>
+    <t>有限会社 ムネケン</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科（リンク先変更前）</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>堀田歯科</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>千歳烏山ケンズ歯科</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>整体処 たくみ堂</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>銀座トレーニングラボ</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>錦糸町矯正歯科クリニック</t>
+  </si>
+  <si>
+    <t>割田歯科医院</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>むぎ歯科</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>はま歯科医院</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>ストレッチ&amp;ボディケア m.o.v.e巣鴨店</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>すがや歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-11-03</t>
+  </si>
+  <si>
+    <t>スカイハイ英語塾</t>
+  </si>
+  <si>
+    <t>きしかわデンタルオフィス</t>
+  </si>
+  <si>
+    <t>2026-11-27</t>
+  </si>
+  <si>
+    <t>UESUGI美容鍼灸整骨院</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>PML　広尾店</t>
+  </si>
+  <si>
+    <t>Healing Salon Ange</t>
+  </si>
+  <si>
+    <t>GAJUM photo studio</t>
+  </si>
+  <si>
+    <t>DesignBody 御徒町店</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>Beauty Salon Arona</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -292,36 +419,36 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -610,14 +737,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:Y31"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y59"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -694,7 +818,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -744,7 +868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -794,7 +918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -844,7 +968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -870,10 +994,10 @@
         <v>3192</v>
       </c>
       <c r="I5">
-        <v>1.463972</v>
+        <v>1.4639720000000001</v>
       </c>
       <c r="J5">
-        <v>50.78350515</v>
+        <v>50.783505150000003</v>
       </c>
       <c r="K5">
         <v>320</v>
@@ -897,28 +1021,28 @@
         <v>97</v>
       </c>
       <c r="S5">
-        <v>50.783505</v>
+        <v>50.783504999999998</v>
       </c>
       <c r="T5">
-        <v>2.075754</v>
+        <v>2.0757539999999999</v>
       </c>
       <c r="U5">
         <v>98</v>
       </c>
       <c r="V5">
-        <v>2.097154</v>
+        <v>2.0971540000000002</v>
       </c>
       <c r="W5">
-        <v>50.265306</v>
+        <v>50.265306000000002</v>
       </c>
       <c r="X5">
         <v>43</v>
       </c>
       <c r="Y5">
-        <v>114.55814</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+        <v>114.55813999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -944,7 +1068,7 @@
         <v>2181</v>
       </c>
       <c r="I6">
-        <v>1.531408</v>
+        <v>1.5314080000000001</v>
       </c>
       <c r="J6">
         <v>38.3046875</v>
@@ -971,7 +1095,7 @@
         <v>128</v>
       </c>
       <c r="S6">
-        <v>38.304688</v>
+        <v>38.304687999999999</v>
       </c>
       <c r="T6">
         <v>3.832335</v>
@@ -980,19 +1104,19 @@
         <v>134</v>
       </c>
       <c r="V6">
-        <v>4.011976</v>
+        <v>4.0119759999999998</v>
       </c>
       <c r="W6">
-        <v>36.589552</v>
+        <v>36.589551999999998</v>
       </c>
       <c r="X6">
         <v>111</v>
       </c>
       <c r="Y6">
-        <v>44.171171</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
+        <v>44.171171000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1021,7 +1145,7 @@
         <v>1.373105</v>
       </c>
       <c r="J7">
-        <v>46.29245283</v>
+        <v>46.292452830000002</v>
       </c>
       <c r="K7">
         <v>160</v>
@@ -1045,7 +1169,7 @@
         <v>106</v>
       </c>
       <c r="S7">
-        <v>46.292453</v>
+        <v>46.292453000000002</v>
       </c>
       <c r="T7">
         <v>3.000283</v>
@@ -1054,19 +1178,19 @@
         <v>113</v>
       </c>
       <c r="V7">
-        <v>3.198415</v>
+        <v>3.1984149999999998</v>
       </c>
       <c r="W7">
-        <v>43.424779</v>
+        <v>43.424779000000001</v>
       </c>
       <c r="X7">
         <v>84</v>
       </c>
       <c r="Y7">
-        <v>58.416667</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
+        <v>58.416666999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1092,10 +1216,10 @@
         <v>3618</v>
       </c>
       <c r="I8">
-        <v>1.519348</v>
+        <v>1.5193479999999999</v>
       </c>
       <c r="J8">
-        <v>41.13333333</v>
+        <v>41.133333329999999</v>
       </c>
       <c r="K8">
         <v>160</v>
@@ -1113,7 +1237,7 @@
         <v>5497</v>
       </c>
       <c r="P8">
-        <v>897.944333</v>
+        <v>897.94433300000003</v>
       </c>
       <c r="Q8">
         <v>120</v>
@@ -1122,13 +1246,13 @@
         <v>41.133333</v>
       </c>
       <c r="T8">
-        <v>2.183009</v>
+        <v>2.1830090000000002</v>
       </c>
       <c r="U8">
         <v>131</v>
       </c>
       <c r="V8">
-        <v>2.383118</v>
+        <v>2.3831180000000001</v>
       </c>
       <c r="W8">
         <v>37.679389</v>
@@ -1137,10 +1261,10 @@
         <v>98</v>
       </c>
       <c r="Y8">
-        <v>50.367347</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
+        <v>50.367347000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1187,34 +1311,34 @@
         <v>5835</v>
       </c>
       <c r="P9">
-        <v>841.988003</v>
+        <v>841.98800300000005</v>
       </c>
       <c r="Q9">
         <v>103</v>
       </c>
       <c r="S9">
-        <v>47.699029</v>
+        <v>47.699029000000003</v>
       </c>
       <c r="T9">
-        <v>1.76521</v>
+        <v>1.7652099999999999</v>
       </c>
       <c r="U9">
         <v>119</v>
       </c>
       <c r="V9">
-        <v>2.039417</v>
+        <v>2.0394169999999998</v>
       </c>
       <c r="W9">
-        <v>41.285714</v>
+        <v>41.285713999999999</v>
       </c>
       <c r="X9">
         <v>77</v>
       </c>
       <c r="Y9">
-        <v>63.805195</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
+        <v>63.805194999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1240,10 +1364,10 @@
         <v>4203</v>
       </c>
       <c r="I10">
-        <v>1.362836</v>
+        <v>1.3628359999999999</v>
       </c>
       <c r="J10">
-        <v>25.9895288</v>
+        <v>25.989528799999999</v>
       </c>
       <c r="K10">
         <v>160</v>
@@ -1261,34 +1385,34 @@
         <v>5728</v>
       </c>
       <c r="P10">
-        <v>866.620112</v>
+        <v>866.62011199999995</v>
       </c>
       <c r="Q10">
         <v>191</v>
       </c>
       <c r="S10">
-        <v>25.989529</v>
+        <v>25.989529000000001</v>
       </c>
       <c r="T10">
-        <v>3.334497</v>
+        <v>3.3344969999999998</v>
       </c>
       <c r="U10">
         <v>225</v>
       </c>
       <c r="V10">
-        <v>3.928073</v>
+        <v>3.9280729999999999</v>
       </c>
       <c r="W10">
-        <v>22.062222</v>
+        <v>22.062221999999998</v>
       </c>
       <c r="X10">
         <v>157</v>
       </c>
       <c r="Y10">
-        <v>31.617834</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+        <v>31.617833999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1317,7 +1441,7 @@
         <v>1.447146</v>
       </c>
       <c r="J11">
-        <v>36.7761194</v>
+        <v>36.776119399999999</v>
       </c>
       <c r="K11">
         <v>160</v>
@@ -1335,13 +1459,13 @@
         <v>6667</v>
       </c>
       <c r="P11">
-        <v>739.163042</v>
+        <v>739.16304200000002</v>
       </c>
       <c r="Q11">
         <v>134</v>
       </c>
       <c r="S11">
-        <v>36.776119</v>
+        <v>36.776119000000001</v>
       </c>
       <c r="T11">
         <v>2.0099</v>
@@ -1350,7 +1474,7 @@
         <v>148</v>
       </c>
       <c r="V11">
-        <v>2.219889</v>
+        <v>2.2198889999999998</v>
       </c>
       <c r="W11">
         <v>33.297297</v>
@@ -1362,7 +1486,7 @@
         <v>49.28</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1415,10 +1539,10 @@
         <v>164</v>
       </c>
       <c r="S12">
-        <v>34.219512</v>
+        <v>34.219512000000002</v>
       </c>
       <c r="T12">
-        <v>1.843111</v>
+        <v>1.8431109999999999</v>
       </c>
       <c r="U12">
         <v>257</v>
@@ -1427,7 +1551,7 @@
         <v>2.88829</v>
       </c>
       <c r="W12">
-        <v>21.836576</v>
+        <v>21.836576000000001</v>
       </c>
       <c r="X12">
         <v>195</v>
@@ -1436,7 +1560,7 @@
         <v>28.779487</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1465,7 +1589,7 @@
         <v>1.684949</v>
       </c>
       <c r="J13">
-        <v>53.40983607</v>
+        <v>53.409836069999997</v>
       </c>
       <c r="K13" t="s">
         <v>34</v>
@@ -1489,28 +1613,28 @@
         <v>114</v>
       </c>
       <c r="S13">
-        <v>57.157895</v>
+        <v>57.157895000000003</v>
       </c>
       <c r="T13">
-        <v>2.208874</v>
+        <v>2.2088739999999998</v>
       </c>
       <c r="U13">
         <v>139</v>
       </c>
       <c r="V13">
-        <v>2.693277</v>
+        <v>2.6932770000000001</v>
       </c>
       <c r="W13">
-        <v>46.877698</v>
+        <v>46.877698000000002</v>
       </c>
       <c r="X13">
         <v>122</v>
       </c>
       <c r="Y13">
-        <v>53.409836</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
+        <v>53.409835999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1539,7 +1663,7 @@
         <v>1.487503</v>
       </c>
       <c r="J14">
-        <v>42.31333333</v>
+        <v>42.313333329999999</v>
       </c>
       <c r="K14" t="s">
         <v>34</v>
@@ -1563,19 +1687,19 @@
         <v>143</v>
       </c>
       <c r="S14">
-        <v>44.384615</v>
+        <v>44.384614999999997</v>
       </c>
       <c r="T14">
-        <v>2.42702</v>
+        <v>2.4270200000000002</v>
       </c>
       <c r="U14">
         <v>152</v>
       </c>
       <c r="V14">
-        <v>2.579769</v>
+        <v>2.5797690000000002</v>
       </c>
       <c r="W14">
-        <v>41.756579</v>
+        <v>41.756579000000002</v>
       </c>
       <c r="X14">
         <v>150</v>
@@ -1584,7 +1708,7 @@
         <v>42.313333</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1613,7 +1737,7 @@
         <v>1.534462</v>
       </c>
       <c r="J15">
-        <v>37.88484848</v>
+        <v>37.884848480000002</v>
       </c>
       <c r="K15" t="s">
         <v>34</v>
@@ -1631,7 +1755,7 @@
         <v>6345</v>
       </c>
       <c r="P15">
-        <v>985.185185</v>
+        <v>985.18518500000005</v>
       </c>
       <c r="Q15">
         <v>158</v>
@@ -1640,25 +1764,25 @@
         <v>39.563291</v>
       </c>
       <c r="T15">
-        <v>2.49015</v>
+        <v>2.4901499999999999</v>
       </c>
       <c r="U15">
         <v>193</v>
       </c>
       <c r="V15">
-        <v>3.041765</v>
+        <v>3.0417649999999998</v>
       </c>
       <c r="W15">
-        <v>32.388601</v>
+        <v>32.388601000000001</v>
       </c>
       <c r="X15">
         <v>165</v>
       </c>
       <c r="Y15">
-        <v>37.884848</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
+        <v>37.884847999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1684,10 +1808,10 @@
         <v>4785</v>
       </c>
       <c r="I16">
-        <v>1.271891</v>
+        <v>1.2718910000000001</v>
       </c>
       <c r="J16">
-        <v>62.71818182</v>
+        <v>62.718181819999998</v>
       </c>
       <c r="K16" t="s">
         <v>34</v>
@@ -1711,28 +1835,28 @@
         <v>113</v>
       </c>
       <c r="S16">
-        <v>61.053097</v>
+        <v>61.053097000000001</v>
       </c>
       <c r="T16">
-        <v>1.85672</v>
+        <v>1.8567199999999999</v>
       </c>
       <c r="U16">
         <v>131</v>
       </c>
       <c r="V16">
-        <v>2.152481</v>
+        <v>2.1524809999999999</v>
       </c>
       <c r="W16">
-        <v>52.664122</v>
+        <v>52.664121999999999</v>
       </c>
       <c r="X16">
         <v>110</v>
       </c>
       <c r="Y16">
-        <v>62.718182</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
+        <v>62.718181999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1761,7 +1885,7 @@
         <v>1.293317</v>
       </c>
       <c r="J17">
-        <v>68.64583333</v>
+        <v>68.645833330000002</v>
       </c>
       <c r="K17" t="s">
         <v>34</v>
@@ -1785,28 +1909,28 @@
         <v>104</v>
       </c>
       <c r="S17">
-        <v>63.365385</v>
+        <v>63.365385000000003</v>
       </c>
       <c r="T17">
-        <v>1.658692</v>
+        <v>1.6586920000000001</v>
       </c>
       <c r="U17">
         <v>133</v>
       </c>
       <c r="V17">
-        <v>2.121212</v>
+        <v>2.1212119999999999</v>
       </c>
       <c r="W17">
-        <v>49.548872</v>
+        <v>49.548872000000003</v>
       </c>
       <c r="X17">
         <v>96</v>
       </c>
       <c r="Y17">
-        <v>68.645833</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
+        <v>68.645832999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1832,10 +1956,10 @@
         <v>4307</v>
       </c>
       <c r="I18">
-        <v>1.367541</v>
+        <v>1.3675409999999999</v>
       </c>
       <c r="J18">
-        <v>46.48550725</v>
+        <v>46.485507249999998</v>
       </c>
       <c r="K18" t="s">
         <v>34</v>
@@ -1853,7 +1977,7 @@
         <v>5890</v>
       </c>
       <c r="P18">
-        <v>1089.134126</v>
+        <v>1089.1341259999999</v>
       </c>
       <c r="Q18">
         <v>134</v>
@@ -1868,19 +1992,19 @@
         <v>145</v>
       </c>
       <c r="V18">
-        <v>2.4618</v>
+        <v>2.4618000000000002</v>
       </c>
       <c r="W18">
-        <v>44.241379</v>
+        <v>44.241379000000002</v>
       </c>
       <c r="X18">
         <v>138</v>
       </c>
       <c r="Y18">
-        <v>46.485507</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25">
+        <v>46.485506999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1930,7 +2054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1956,10 +2080,10 @@
         <v>4010</v>
       </c>
       <c r="I20">
-        <v>1.75212</v>
+        <v>1.7521199999999999</v>
       </c>
       <c r="J20">
-        <v>44.10869565</v>
+        <v>44.108695650000001</v>
       </c>
       <c r="K20" t="s">
         <v>34</v>
@@ -1977,34 +2101,34 @@
         <v>7026</v>
       </c>
       <c r="P20">
-        <v>866.353544</v>
+        <v>866.35354400000006</v>
       </c>
       <c r="Q20">
         <v>158</v>
       </c>
       <c r="S20">
-        <v>38.525316</v>
+        <v>38.525315999999997</v>
       </c>
       <c r="T20">
-        <v>2.24879</v>
+        <v>2.2487900000000001</v>
       </c>
       <c r="U20">
         <v>186</v>
       </c>
       <c r="V20">
-        <v>2.64731</v>
+        <v>2.6473100000000001</v>
       </c>
       <c r="W20">
-        <v>32.725806</v>
+        <v>32.725805999999999</v>
       </c>
       <c r="X20">
         <v>138</v>
       </c>
       <c r="Y20">
-        <v>44.108696</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25">
+        <v>44.108696000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -2030,10 +2154,10 @@
         <v>3996</v>
       </c>
       <c r="I21">
-        <v>1.774525</v>
+        <v>1.7745249999999999</v>
       </c>
       <c r="J21">
-        <v>32.58695652</v>
+        <v>32.586956520000001</v>
       </c>
       <c r="K21" t="s">
         <v>34</v>
@@ -2051,7 +2175,7 @@
         <v>7091</v>
       </c>
       <c r="P21">
-        <v>845.578903</v>
+        <v>845.57890299999997</v>
       </c>
       <c r="Q21">
         <v>216</v>
@@ -2060,7 +2184,7 @@
         <v>27.759259</v>
       </c>
       <c r="T21">
-        <v>3.046115</v>
+        <v>3.0461149999999999</v>
       </c>
       <c r="U21">
         <v>251</v>
@@ -2069,16 +2193,16 @@
         <v>3.539698</v>
       </c>
       <c r="W21">
-        <v>23.888446</v>
+        <v>23.888445999999998</v>
       </c>
       <c r="X21">
         <v>184</v>
       </c>
       <c r="Y21">
-        <v>32.586957</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
+        <v>32.586956999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -2104,10 +2228,10 @@
         <v>4211</v>
       </c>
       <c r="I22">
-        <v>1.71337</v>
+        <v>1.7133700000000001</v>
       </c>
       <c r="J22">
-        <v>58.06603774</v>
+        <v>58.066037739999999</v>
       </c>
       <c r="K22" t="s">
         <v>34</v>
@@ -2125,34 +2249,34 @@
         <v>7215</v>
       </c>
       <c r="P22">
-        <v>853.083853</v>
+        <v>853.08385299999998</v>
       </c>
       <c r="Q22">
         <v>118</v>
       </c>
       <c r="S22">
-        <v>52.161017</v>
+        <v>52.161017000000001</v>
       </c>
       <c r="T22">
-        <v>1.635482</v>
+        <v>1.6354820000000001</v>
       </c>
       <c r="U22">
         <v>161</v>
       </c>
       <c r="V22">
-        <v>2.231462</v>
+        <v>2.2314620000000001</v>
       </c>
       <c r="W22">
-        <v>38.229814</v>
+        <v>38.229813999999998</v>
       </c>
       <c r="X22">
         <v>106</v>
       </c>
       <c r="Y22">
-        <v>58.066038</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25">
+        <v>58.066037999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -2178,10 +2302,10 @@
         <v>3350</v>
       </c>
       <c r="I23">
-        <v>2.116119</v>
+        <v>2.1161189999999999</v>
       </c>
       <c r="J23">
-        <v>98.33846154</v>
+        <v>98.338461539999997</v>
       </c>
       <c r="K23" t="s">
         <v>34</v>
@@ -2199,13 +2323,13 @@
         <v>7089</v>
       </c>
       <c r="P23">
-        <v>901.678657</v>
+        <v>901.67865700000004</v>
       </c>
       <c r="Q23">
         <v>74</v>
       </c>
       <c r="S23">
-        <v>86.378378</v>
+        <v>86.378377999999998</v>
       </c>
       <c r="T23">
         <v>1.043871</v>
@@ -2214,19 +2338,19 @@
         <v>84</v>
       </c>
       <c r="V23">
-        <v>1.184934</v>
+        <v>1.1849339999999999</v>
       </c>
       <c r="W23">
-        <v>76.095238</v>
+        <v>76.095237999999995</v>
       </c>
       <c r="X23">
         <v>65</v>
       </c>
       <c r="Y23">
-        <v>98.338462</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25">
+        <v>98.338462000000007</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2252,10 +2376,10 @@
         <v>3549</v>
       </c>
       <c r="I24">
-        <v>1.73401</v>
+        <v>1.7340100000000001</v>
       </c>
       <c r="J24">
-        <v>54.12068966</v>
+        <v>54.120689659999996</v>
       </c>
       <c r="K24" t="s">
         <v>34</v>
@@ -2279,7 +2403,7 @@
         <v>125</v>
       </c>
       <c r="S24">
-        <v>50.224</v>
+        <v>50.223999999999997</v>
       </c>
       <c r="T24">
         <v>2.031199</v>
@@ -2288,19 +2412,19 @@
         <v>143</v>
       </c>
       <c r="V24">
-        <v>2.323692</v>
+        <v>2.3236919999999999</v>
       </c>
       <c r="W24">
-        <v>43.902098</v>
+        <v>43.902098000000002</v>
       </c>
       <c r="X24">
         <v>116</v>
       </c>
       <c r="Y24">
-        <v>54.12069</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25">
+        <v>54.120690000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2329,7 +2453,7 @@
         <v>1.538951</v>
       </c>
       <c r="J25">
-        <v>24.31698113</v>
+        <v>24.316981129999999</v>
       </c>
       <c r="K25" t="s">
         <v>34</v>
@@ -2353,28 +2477,28 @@
         <v>276</v>
       </c>
       <c r="S25">
-        <v>23.347826</v>
+        <v>23.347826000000001</v>
       </c>
       <c r="T25">
-        <v>5.702479</v>
+        <v>5.7024790000000003</v>
       </c>
       <c r="U25">
         <v>318</v>
       </c>
       <c r="V25">
-        <v>6.570248</v>
+        <v>6.5702480000000003</v>
       </c>
       <c r="W25">
-        <v>20.264151</v>
+        <v>20.264150999999998</v>
       </c>
       <c r="X25">
         <v>265</v>
       </c>
       <c r="Y25">
-        <v>24.316981</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25">
+        <v>24.316980999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2424,7 +2548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2474,7 +2598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -2524,7 +2648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -2550,10 +2674,10 @@
         <v>4046</v>
       </c>
       <c r="I29">
-        <v>1.851705</v>
+        <v>1.8517049999999999</v>
       </c>
       <c r="J29">
-        <v>70.66304348</v>
+        <v>70.663043479999999</v>
       </c>
       <c r="K29" t="s">
         <v>34</v>
@@ -2571,16 +2695,16 @@
         <v>7492</v>
       </c>
       <c r="P29">
-        <v>867.725574</v>
+        <v>867.72557400000005</v>
       </c>
       <c r="Q29">
         <v>97</v>
       </c>
       <c r="S29">
-        <v>67.020619</v>
+        <v>67.020618999999996</v>
       </c>
       <c r="T29">
-        <v>1.294714</v>
+        <v>1.2947139999999999</v>
       </c>
       <c r="U29">
         <v>112</v>
@@ -2589,16 +2713,16 @@
         <v>1.494928</v>
       </c>
       <c r="W29">
-        <v>58.044643</v>
+        <v>58.044643000000001</v>
       </c>
       <c r="X29">
         <v>92</v>
       </c>
       <c r="Y29">
-        <v>70.663043</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25">
+        <v>70.663043000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -2624,7 +2748,7 @@
         <v>3136</v>
       </c>
       <c r="I30">
-        <v>1.536352</v>
+        <v>1.5363519999999999</v>
       </c>
       <c r="J30">
         <v>46</v>
@@ -2645,13 +2769,13 @@
         <v>4818</v>
       </c>
       <c r="P30">
-        <v>1365.296804</v>
+        <v>1365.2968040000001</v>
       </c>
       <c r="Q30">
         <v>147</v>
       </c>
       <c r="S30">
-        <v>44.748299</v>
+        <v>44.748299000000003</v>
       </c>
       <c r="T30">
         <v>3.051059</v>
@@ -2660,10 +2784,10 @@
         <v>161</v>
       </c>
       <c r="V30">
-        <v>3.341636</v>
+        <v>3.3416359999999998</v>
       </c>
       <c r="W30">
-        <v>40.857143</v>
+        <v>40.857143000000001</v>
       </c>
       <c r="X30">
         <v>143</v>
@@ -2672,7 +2796,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -2698,10 +2822,10 @@
         <v>2325</v>
       </c>
       <c r="I31">
-        <v>1.875269</v>
+        <v>1.8752690000000001</v>
       </c>
       <c r="J31">
-        <v>31.90178571</v>
+        <v>31.901785709999999</v>
       </c>
       <c r="K31" t="s">
         <v>34</v>
@@ -2719,45 +2843,1976 @@
         <v>4360</v>
       </c>
       <c r="P31">
-        <v>819.495413</v>
+        <v>819.49541299999999</v>
       </c>
       <c r="Q31">
         <v>90</v>
       </c>
       <c r="S31">
-        <v>39.7</v>
+        <v>39.700000000000003</v>
       </c>
       <c r="T31">
-        <v>2.06422</v>
+        <v>2.0642200000000002</v>
       </c>
       <c r="U31">
         <v>141</v>
       </c>
       <c r="V31">
-        <v>3.233945</v>
+        <v>3.2339449999999998</v>
       </c>
       <c r="W31">
-        <v>25.340426</v>
+        <v>25.340426000000001</v>
       </c>
       <c r="X31">
         <v>112</v>
       </c>
       <c r="Y31">
-        <v>31.901786</v>
+        <v>31.901786000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32">
+        <v>55</v>
+      </c>
+      <c r="G32" t="s">
+        <v>49</v>
+      </c>
+      <c r="H32">
+        <v>3412</v>
+      </c>
+      <c r="I32">
+        <v>1.9818290000000001</v>
+      </c>
+      <c r="J32">
+        <v>123.81818182000001</v>
+      </c>
+      <c r="K32" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>6810</v>
+      </c>
+      <c r="N32" t="s">
+        <v>65</v>
+      </c>
+      <c r="O32">
+        <v>6762</v>
+      </c>
+      <c r="P32">
+        <v>1007.098492</v>
+      </c>
+      <c r="Q32">
+        <v>99</v>
+      </c>
+      <c r="S32">
+        <v>68.787879000000004</v>
+      </c>
+      <c r="T32">
+        <v>1.464064</v>
+      </c>
+      <c r="U32">
+        <v>151</v>
+      </c>
+      <c r="V32">
+        <v>2.2330670000000001</v>
+      </c>
+      <c r="W32">
+        <v>45.099338000000003</v>
+      </c>
+      <c r="X32">
+        <v>55</v>
+      </c>
+      <c r="Y32">
+        <v>123.81818199999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33">
+        <v>157</v>
+      </c>
+      <c r="G33" t="s">
+        <v>39</v>
+      </c>
+      <c r="H33">
+        <v>2670</v>
+      </c>
+      <c r="I33">
+        <v>1.376779</v>
+      </c>
+      <c r="J33">
+        <v>35.197452230000003</v>
+      </c>
+      <c r="K33" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>5526</v>
+      </c>
+      <c r="N33" t="s">
+        <v>120</v>
+      </c>
+      <c r="O33">
+        <v>3676</v>
+      </c>
+      <c r="P33">
+        <v>1503.264418</v>
+      </c>
+      <c r="Q33">
+        <v>157</v>
+      </c>
+      <c r="S33">
+        <v>35.197451999999998</v>
+      </c>
+      <c r="T33">
+        <v>4.2709469999999996</v>
+      </c>
+      <c r="U33">
+        <v>163</v>
+      </c>
+      <c r="V33">
+        <v>4.4341679999999997</v>
+      </c>
+      <c r="W33">
+        <v>33.90184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34">
+        <v>98</v>
+      </c>
+      <c r="G34" t="s">
+        <v>49</v>
+      </c>
+      <c r="H34">
+        <v>4180</v>
+      </c>
+      <c r="I34">
+        <v>1.671292</v>
+      </c>
+      <c r="J34">
+        <v>68.193877549999996</v>
+      </c>
+      <c r="K34" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>6683</v>
+      </c>
+      <c r="N34" t="s">
+        <v>115</v>
+      </c>
+      <c r="O34">
+        <v>6986</v>
+      </c>
+      <c r="P34">
+        <v>956.62754099999995</v>
+      </c>
+      <c r="Q34">
+        <v>122</v>
+      </c>
+      <c r="S34">
+        <v>54.778689</v>
+      </c>
+      <c r="T34">
+        <v>1.7463500000000001</v>
+      </c>
+      <c r="U34">
+        <v>134</v>
+      </c>
+      <c r="V34">
+        <v>1.9181220000000001</v>
+      </c>
+      <c r="W34">
+        <v>49.873134</v>
+      </c>
+      <c r="X34">
+        <v>98</v>
+      </c>
+      <c r="Y34">
+        <v>68.193877999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" t="s">
+        <v>83</v>
+      </c>
+      <c r="E35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35">
+        <v>86</v>
+      </c>
+      <c r="G35" t="s">
+        <v>39</v>
+      </c>
+      <c r="H35">
+        <v>5240</v>
+      </c>
+      <c r="I35">
+        <v>1.6099239999999999</v>
+      </c>
+      <c r="J35">
+        <v>63.406976739999998</v>
+      </c>
+      <c r="K35" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>5453</v>
+      </c>
+      <c r="N35" t="s">
+        <v>106</v>
+      </c>
+      <c r="O35">
+        <v>8436</v>
+      </c>
+      <c r="P35">
+        <v>646.39639599999998</v>
+      </c>
+      <c r="Q35">
+        <v>86</v>
+      </c>
+      <c r="S35">
+        <v>63.406976999999998</v>
+      </c>
+      <c r="T35">
+        <v>1.0194399999999999</v>
+      </c>
+      <c r="U35">
+        <v>91</v>
+      </c>
+      <c r="V35">
+        <v>1.0787100000000001</v>
+      </c>
+      <c r="W35">
+        <v>59.923076999999999</v>
+      </c>
+      <c r="X35">
+        <v>59</v>
+      </c>
+      <c r="Y35">
+        <v>92.423728999999994</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" t="s">
+        <v>117</v>
+      </c>
+      <c r="D36" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36">
+        <v>83</v>
+      </c>
+      <c r="G36" t="s">
+        <v>49</v>
+      </c>
+      <c r="H36">
+        <v>3279</v>
+      </c>
+      <c r="I36">
+        <v>1.642879</v>
+      </c>
+      <c r="J36">
+        <v>85.09638554</v>
+      </c>
+      <c r="K36" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>7063</v>
+      </c>
+      <c r="N36" t="s">
+        <v>76</v>
+      </c>
+      <c r="O36">
+        <v>5387</v>
+      </c>
+      <c r="P36">
+        <v>1311.119361</v>
+      </c>
+      <c r="Q36">
+        <v>172</v>
+      </c>
+      <c r="S36">
+        <v>41.063952999999998</v>
+      </c>
+      <c r="T36">
+        <v>3.1928719999999999</v>
+      </c>
+      <c r="U36">
+        <v>212</v>
+      </c>
+      <c r="V36">
+        <v>3.9354</v>
+      </c>
+      <c r="W36">
+        <v>33.316037999999999</v>
+      </c>
+      <c r="X36">
+        <v>83</v>
+      </c>
+      <c r="Y36">
+        <v>85.096385999999995</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="K37" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>115</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38">
+        <v>130</v>
+      </c>
+      <c r="G38" t="s">
+        <v>49</v>
+      </c>
+      <c r="H38">
+        <v>3340</v>
+      </c>
+      <c r="I38">
+        <v>1.5892219999999999</v>
+      </c>
+      <c r="J38">
+        <v>51.630769229999999</v>
+      </c>
+      <c r="K38" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>6712</v>
+      </c>
+      <c r="N38" t="s">
+        <v>63</v>
+      </c>
+      <c r="O38">
+        <v>5308</v>
+      </c>
+      <c r="P38">
+        <v>1264.5064050000001</v>
+      </c>
+      <c r="Q38">
+        <v>128</v>
+      </c>
+      <c r="S38">
+        <v>52.4375</v>
+      </c>
+      <c r="T38">
+        <v>2.411454</v>
+      </c>
+      <c r="U38">
+        <v>146</v>
+      </c>
+      <c r="V38">
+        <v>2.7505649999999999</v>
+      </c>
+      <c r="W38">
+        <v>45.972602999999999</v>
+      </c>
+      <c r="X38">
+        <v>130</v>
+      </c>
+      <c r="Y38">
+        <v>51.630769000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" t="s">
+        <v>71</v>
+      </c>
+      <c r="D39" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39">
+        <v>532</v>
+      </c>
+      <c r="G39" t="s">
+        <v>49</v>
+      </c>
+      <c r="H39">
+        <v>9793</v>
+      </c>
+      <c r="I39">
+        <v>1.587256</v>
+      </c>
+      <c r="J39">
+        <v>47.103383460000003</v>
+      </c>
+      <c r="K39" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>25059</v>
+      </c>
+      <c r="N39" t="s">
+        <v>113</v>
+      </c>
+      <c r="O39">
+        <v>15544</v>
+      </c>
+      <c r="P39">
+        <v>1612.1332990000001</v>
+      </c>
+      <c r="Q39">
+        <v>536</v>
+      </c>
+      <c r="S39">
+        <v>46.751866</v>
+      </c>
+      <c r="T39">
+        <v>3.4482759999999999</v>
+      </c>
+      <c r="U39">
+        <v>633</v>
+      </c>
+      <c r="V39">
+        <v>4.072311</v>
+      </c>
+      <c r="W39">
+        <v>39.587677999999997</v>
+      </c>
+      <c r="X39">
+        <v>532</v>
+      </c>
+      <c r="Y39">
+        <v>47.103383000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" t="s">
+        <v>29</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="s">
+        <v>34</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>81</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" t="s">
+        <v>38</v>
+      </c>
+      <c r="E41" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41">
+        <v>38</v>
+      </c>
+      <c r="G41" t="s">
+        <v>49</v>
+      </c>
+      <c r="H41">
+        <v>3934</v>
+      </c>
+      <c r="I41">
+        <v>1.5833759999999999</v>
+      </c>
+      <c r="J41">
+        <v>155.65789473999999</v>
+      </c>
+      <c r="K41" t="s">
+        <v>34</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>5915</v>
+      </c>
+      <c r="N41" t="s">
+        <v>110</v>
+      </c>
+      <c r="O41">
+        <v>6229</v>
+      </c>
+      <c r="P41">
+        <v>949.59062500000005</v>
+      </c>
+      <c r="Q41">
+        <v>209</v>
+      </c>
+      <c r="S41">
+        <v>28.301435000000001</v>
+      </c>
+      <c r="T41">
+        <v>3.3552740000000001</v>
+      </c>
+      <c r="U41">
+        <v>222</v>
+      </c>
+      <c r="V41">
+        <v>3.5639750000000001</v>
+      </c>
+      <c r="W41">
+        <v>26.644144000000001</v>
+      </c>
+      <c r="X41">
+        <v>38</v>
+      </c>
+      <c r="Y41">
+        <v>155.657895</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" t="s">
+        <v>38</v>
+      </c>
+      <c r="E42" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42">
+        <v>128</v>
+      </c>
+      <c r="G42" t="s">
+        <v>39</v>
+      </c>
+      <c r="H42">
+        <v>4597</v>
+      </c>
+      <c r="I42">
+        <v>1.81836</v>
+      </c>
+      <c r="J42">
+        <v>43.796875</v>
+      </c>
+      <c r="K42" t="s">
+        <v>34</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>5606</v>
+      </c>
+      <c r="N42" t="s">
+        <v>108</v>
+      </c>
+      <c r="O42">
+        <v>8359</v>
+      </c>
+      <c r="P42">
+        <v>670.65438500000005</v>
+      </c>
+      <c r="Q42">
+        <v>128</v>
+      </c>
+      <c r="S42">
+        <v>43.796875</v>
+      </c>
+      <c r="T42">
+        <v>1.5312840000000001</v>
+      </c>
+      <c r="U42">
+        <v>150</v>
+      </c>
+      <c r="V42">
+        <v>1.794473</v>
+      </c>
+      <c r="W42">
+        <v>37.373333000000002</v>
+      </c>
+      <c r="X42">
+        <v>118</v>
+      </c>
+      <c r="Y42">
+        <v>47.508474999999997</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" t="s">
+        <v>107</v>
+      </c>
+      <c r="D43" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" t="s">
+        <v>29</v>
+      </c>
+      <c r="F43">
+        <v>221</v>
+      </c>
+      <c r="G43" t="s">
+        <v>39</v>
+      </c>
+      <c r="H43">
+        <v>2959</v>
+      </c>
+      <c r="I43">
+        <v>1.384927</v>
+      </c>
+      <c r="J43">
+        <v>25.429864250000001</v>
+      </c>
+      <c r="K43" t="s">
+        <v>34</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>5620</v>
+      </c>
+      <c r="N43" t="s">
+        <v>106</v>
+      </c>
+      <c r="O43">
+        <v>4098</v>
+      </c>
+      <c r="P43">
+        <v>1371.4006830000001</v>
+      </c>
+      <c r="Q43">
+        <v>221</v>
+      </c>
+      <c r="S43">
+        <v>25.429863999999998</v>
+      </c>
+      <c r="T43">
+        <v>5.3928750000000001</v>
+      </c>
+      <c r="U43">
+        <v>241</v>
+      </c>
+      <c r="V43">
+        <v>5.8809180000000003</v>
+      </c>
+      <c r="W43">
+        <v>23.319502</v>
+      </c>
+      <c r="X43">
+        <v>198</v>
+      </c>
+      <c r="Y43">
+        <v>28.383838000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" t="s">
+        <v>83</v>
+      </c>
+      <c r="E44" t="s">
+        <v>29</v>
+      </c>
+      <c r="F44">
+        <v>217</v>
+      </c>
+      <c r="G44" t="s">
+        <v>39</v>
+      </c>
+      <c r="H44">
+        <v>3444</v>
+      </c>
+      <c r="I44">
+        <v>1.3391409999999999</v>
+      </c>
+      <c r="J44">
+        <v>24.894009220000001</v>
+      </c>
+      <c r="K44" t="s">
+        <v>34</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>5402</v>
+      </c>
+      <c r="N44" t="s">
+        <v>94</v>
+      </c>
+      <c r="O44">
+        <v>4612</v>
+      </c>
+      <c r="P44">
+        <v>1171.292281</v>
+      </c>
+      <c r="Q44">
+        <v>217</v>
+      </c>
+      <c r="S44">
+        <v>24.894009</v>
+      </c>
+      <c r="T44">
+        <v>4.7051170000000004</v>
+      </c>
+      <c r="U44">
+        <v>219</v>
+      </c>
+      <c r="V44">
+        <v>4.7484820000000001</v>
+      </c>
+      <c r="W44">
+        <v>24.666667</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" t="s">
+        <v>104</v>
+      </c>
+      <c r="D45" t="s">
+        <v>38</v>
+      </c>
+      <c r="E45" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45">
+        <v>109</v>
+      </c>
+      <c r="G45" t="s">
+        <v>39</v>
+      </c>
+      <c r="H45">
+        <v>4684</v>
+      </c>
+      <c r="I45">
+        <v>1.7032449999999999</v>
+      </c>
+      <c r="J45">
+        <v>55.577981649999998</v>
+      </c>
+      <c r="K45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>6058</v>
+      </c>
+      <c r="N45" t="s">
+        <v>103</v>
+      </c>
+      <c r="O45">
+        <v>7978</v>
+      </c>
+      <c r="P45">
+        <v>759.33817999999997</v>
+      </c>
+      <c r="Q45">
+        <v>109</v>
+      </c>
+      <c r="S45">
+        <v>55.577981999999999</v>
+      </c>
+      <c r="T45">
+        <v>1.3662570000000001</v>
+      </c>
+      <c r="U45">
+        <v>119</v>
+      </c>
+      <c r="V45">
+        <v>1.4916020000000001</v>
+      </c>
+      <c r="W45">
+        <v>50.907563000000003</v>
+      </c>
+      <c r="X45">
+        <v>52</v>
+      </c>
+      <c r="Y45">
+        <v>116.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" t="s">
+        <v>102</v>
+      </c>
+      <c r="D46" t="s">
+        <v>83</v>
+      </c>
+      <c r="E46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F46">
+        <v>284</v>
+      </c>
+      <c r="G46" t="s">
+        <v>39</v>
+      </c>
+      <c r="H46">
+        <v>3702</v>
+      </c>
+      <c r="I46">
+        <v>1.300918</v>
+      </c>
+      <c r="J46">
+        <v>18.609154929999999</v>
+      </c>
+      <c r="K46" t="s">
+        <v>34</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>5285</v>
+      </c>
+      <c r="N46" t="s">
+        <v>85</v>
+      </c>
+      <c r="O46">
+        <v>4816</v>
+      </c>
+      <c r="P46">
+        <v>1097.3837209999999</v>
+      </c>
+      <c r="Q46">
+        <v>284</v>
+      </c>
+      <c r="S46">
+        <v>18.609155000000001</v>
+      </c>
+      <c r="T46">
+        <v>5.8970099999999999</v>
+      </c>
+      <c r="U46">
+        <v>292</v>
+      </c>
+      <c r="V46">
+        <v>6.063123</v>
+      </c>
+      <c r="W46">
+        <v>18.099315000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" t="s">
+        <v>38</v>
+      </c>
+      <c r="E47" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47">
+        <v>238</v>
+      </c>
+      <c r="G47" t="s">
+        <v>39</v>
+      </c>
+      <c r="H47">
+        <v>3690</v>
+      </c>
+      <c r="I47">
+        <v>1.598374</v>
+      </c>
+      <c r="J47">
+        <v>23.756302519999998</v>
+      </c>
+      <c r="K47" t="s">
+        <v>34</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>5654</v>
+      </c>
+      <c r="N47" t="s">
+        <v>100</v>
+      </c>
+      <c r="O47">
+        <v>5898</v>
+      </c>
+      <c r="P47">
+        <v>958.630044</v>
+      </c>
+      <c r="Q47">
+        <v>238</v>
+      </c>
+      <c r="S47">
+        <v>23.756302999999999</v>
+      </c>
+      <c r="T47">
+        <v>4.035266</v>
+      </c>
+      <c r="U47">
+        <v>246</v>
+      </c>
+      <c r="V47">
+        <v>4.1709050000000003</v>
+      </c>
+      <c r="W47">
+        <v>22.983740000000001</v>
+      </c>
+      <c r="X47">
+        <v>215</v>
+      </c>
+      <c r="Y47">
+        <v>26.297674000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" t="s">
+        <v>99</v>
+      </c>
+      <c r="D48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E48" t="s">
+        <v>29</v>
+      </c>
+      <c r="F48">
+        <v>139</v>
+      </c>
+      <c r="G48" t="s">
+        <v>39</v>
+      </c>
+      <c r="H48">
+        <v>3365</v>
+      </c>
+      <c r="I48">
+        <v>1.630906</v>
+      </c>
+      <c r="J48">
+        <v>39.223021580000001</v>
+      </c>
+      <c r="K48" t="s">
+        <v>34</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>5452</v>
+      </c>
+      <c r="N48" t="s">
+        <v>94</v>
+      </c>
+      <c r="O48">
+        <v>5488</v>
+      </c>
+      <c r="P48">
+        <v>993.44023300000003</v>
+      </c>
+      <c r="Q48">
+        <v>139</v>
+      </c>
+      <c r="S48">
+        <v>39.223022</v>
+      </c>
+      <c r="T48">
+        <v>2.5327989999999998</v>
+      </c>
+      <c r="U48">
+        <v>160</v>
+      </c>
+      <c r="V48">
+        <v>2.9154520000000002</v>
+      </c>
+      <c r="W48">
+        <v>34.075000000000003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" t="s">
+        <v>29</v>
+      </c>
+      <c r="F49">
+        <v>217</v>
+      </c>
+      <c r="G49" t="s">
+        <v>39</v>
+      </c>
+      <c r="H49">
+        <v>4097</v>
+      </c>
+      <c r="I49">
+        <v>1.3897969999999999</v>
+      </c>
+      <c r="J49">
+        <v>26.442396309999999</v>
+      </c>
+      <c r="K49" t="s">
+        <v>34</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>5738</v>
+      </c>
+      <c r="N49" t="s">
+        <v>97</v>
+      </c>
+      <c r="O49">
+        <v>5694</v>
+      </c>
+      <c r="P49">
+        <v>1007.727432</v>
+      </c>
+      <c r="Q49">
+        <v>217</v>
+      </c>
+      <c r="S49">
+        <v>26.442395999999999</v>
+      </c>
+      <c r="T49">
+        <v>3.811029</v>
+      </c>
+      <c r="U49">
+        <v>286</v>
+      </c>
+      <c r="V49">
+        <v>5.022831</v>
+      </c>
+      <c r="W49">
+        <v>20.062937000000002</v>
+      </c>
+      <c r="X49">
+        <v>210</v>
+      </c>
+      <c r="Y49">
+        <v>27.323810000000002</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" t="s">
+        <v>96</v>
+      </c>
+      <c r="D50" t="s">
+        <v>83</v>
+      </c>
+      <c r="E50" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50">
+        <v>70</v>
+      </c>
+      <c r="G50" t="s">
+        <v>39</v>
+      </c>
+      <c r="H50">
+        <v>2071</v>
+      </c>
+      <c r="I50">
+        <v>2.998551</v>
+      </c>
+      <c r="J50">
+        <v>74.02857143</v>
+      </c>
+      <c r="K50" t="s">
+        <v>34</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>5182</v>
+      </c>
+      <c r="N50" t="s">
+        <v>35</v>
+      </c>
+      <c r="O50">
+        <v>6210</v>
+      </c>
+      <c r="P50">
+        <v>834.46054800000002</v>
+      </c>
+      <c r="Q50">
+        <v>70</v>
+      </c>
+      <c r="S50">
+        <v>74.028570999999999</v>
+      </c>
+      <c r="T50">
+        <v>1.1272139999999999</v>
+      </c>
+      <c r="U50">
+        <v>71</v>
+      </c>
+      <c r="V50">
+        <v>1.1433169999999999</v>
+      </c>
+      <c r="W50">
+        <v>72.985915000000006</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" t="s">
+        <v>95</v>
+      </c>
+      <c r="D51" t="s">
+        <v>83</v>
+      </c>
+      <c r="E51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51">
+        <v>116</v>
+      </c>
+      <c r="G51" t="s">
+        <v>39</v>
+      </c>
+      <c r="H51">
+        <v>3795</v>
+      </c>
+      <c r="I51">
+        <v>1.3976280000000001</v>
+      </c>
+      <c r="J51">
+        <v>48.413793099999999</v>
+      </c>
+      <c r="K51" t="s">
+        <v>34</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>5616</v>
+      </c>
+      <c r="N51" t="s">
+        <v>94</v>
+      </c>
+      <c r="O51">
+        <v>5304</v>
+      </c>
+      <c r="P51">
+        <v>1058.823529</v>
+      </c>
+      <c r="Q51">
+        <v>116</v>
+      </c>
+      <c r="S51">
+        <v>48.413792999999998</v>
+      </c>
+      <c r="T51">
+        <v>2.1870289999999999</v>
+      </c>
+      <c r="U51">
+        <v>121</v>
+      </c>
+      <c r="V51">
+        <v>2.2812969999999999</v>
+      </c>
+      <c r="W51">
+        <v>46.413223000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" t="s">
+        <v>93</v>
+      </c>
+      <c r="D52" t="s">
+        <v>38</v>
+      </c>
+      <c r="E52" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52">
+        <v>140</v>
+      </c>
+      <c r="G52" t="s">
+        <v>39</v>
+      </c>
+      <c r="H52">
+        <v>2155</v>
+      </c>
+      <c r="I52">
+        <v>1.3823669999999999</v>
+      </c>
+      <c r="J52">
+        <v>44.678571429999998</v>
+      </c>
+      <c r="K52" t="s">
+        <v>34</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>6255</v>
+      </c>
+      <c r="N52" t="s">
+        <v>92</v>
+      </c>
+      <c r="O52">
+        <v>2979</v>
+      </c>
+      <c r="P52">
+        <v>2099.697885</v>
+      </c>
+      <c r="Q52">
+        <v>140</v>
+      </c>
+      <c r="S52">
+        <v>44.678570999999998</v>
+      </c>
+      <c r="T52">
+        <v>4.6995639999999996</v>
+      </c>
+      <c r="U52">
+        <v>147</v>
+      </c>
+      <c r="V52">
+        <v>4.9345420000000004</v>
+      </c>
+      <c r="W52">
+        <v>42.551020000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" t="s">
+        <v>91</v>
+      </c>
+      <c r="D53" t="s">
+        <v>83</v>
+      </c>
+      <c r="E53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F53">
+        <v>111</v>
+      </c>
+      <c r="G53" t="s">
+        <v>39</v>
+      </c>
+      <c r="H53">
+        <v>3887</v>
+      </c>
+      <c r="I53">
+        <v>1.4394130000000001</v>
+      </c>
+      <c r="J53">
+        <v>51.531531530000002</v>
+      </c>
+      <c r="K53" t="s">
+        <v>34</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>5720</v>
+      </c>
+      <c r="N53" t="s">
+        <v>90</v>
+      </c>
+      <c r="O53">
+        <v>5595</v>
+      </c>
+      <c r="P53">
+        <v>1022.341376</v>
+      </c>
+      <c r="Q53">
+        <v>111</v>
+      </c>
+      <c r="S53">
+        <v>51.531531999999999</v>
+      </c>
+      <c r="T53">
+        <v>1.983914</v>
+      </c>
+      <c r="U53">
+        <v>116</v>
+      </c>
+      <c r="V53">
+        <v>2.07328</v>
+      </c>
+      <c r="W53">
+        <v>49.310344999999998</v>
+      </c>
+      <c r="X53">
+        <v>90</v>
+      </c>
+      <c r="Y53">
+        <v>63.555556000000003</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" t="s">
+        <v>89</v>
+      </c>
+      <c r="D54" t="s">
+        <v>28</v>
+      </c>
+      <c r="E54" t="s">
+        <v>29</v>
+      </c>
+      <c r="F54">
+        <v>82</v>
+      </c>
+      <c r="G54" t="s">
+        <v>39</v>
+      </c>
+      <c r="H54">
+        <v>3654</v>
+      </c>
+      <c r="I54">
+        <v>1.266284</v>
+      </c>
+      <c r="J54">
+        <v>56.695121950000001</v>
+      </c>
+      <c r="K54" t="s">
+        <v>34</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>4649</v>
+      </c>
+      <c r="N54" t="s">
+        <v>88</v>
+      </c>
+      <c r="O54">
+        <v>4627</v>
+      </c>
+      <c r="P54">
+        <v>1004.754701</v>
+      </c>
+      <c r="Q54">
+        <v>82</v>
+      </c>
+      <c r="S54">
+        <v>56.695121999999998</v>
+      </c>
+      <c r="T54">
+        <v>1.7722070000000001</v>
+      </c>
+      <c r="U54">
+        <v>87</v>
+      </c>
+      <c r="V54">
+        <v>1.8802680000000001</v>
+      </c>
+      <c r="W54">
+        <v>53.436782000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" t="s">
+        <v>32</v>
+      </c>
+      <c r="D55" t="s">
+        <v>83</v>
+      </c>
+      <c r="E55" t="s">
+        <v>29</v>
+      </c>
+      <c r="F55">
+        <v>94</v>
+      </c>
+      <c r="G55" t="s">
+        <v>39</v>
+      </c>
+      <c r="H55">
+        <v>3444</v>
+      </c>
+      <c r="I55">
+        <v>1.263647</v>
+      </c>
+      <c r="J55">
+        <v>60</v>
+      </c>
+      <c r="K55" t="s">
+        <v>34</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>5640</v>
+      </c>
+      <c r="N55" t="s">
+        <v>87</v>
+      </c>
+      <c r="O55">
+        <v>4352</v>
+      </c>
+      <c r="P55">
+        <v>1295.955882</v>
+      </c>
+      <c r="Q55">
+        <v>94</v>
+      </c>
+      <c r="S55">
+        <v>60</v>
+      </c>
+      <c r="T55">
+        <v>2.159926</v>
+      </c>
+      <c r="U55">
+        <v>104</v>
+      </c>
+      <c r="V55">
+        <v>2.3897059999999999</v>
+      </c>
+      <c r="W55">
+        <v>54.230769000000002</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" t="s">
+        <v>86</v>
+      </c>
+      <c r="D56" t="s">
+        <v>83</v>
+      </c>
+      <c r="E56" t="s">
+        <v>29</v>
+      </c>
+      <c r="F56">
+        <v>109</v>
+      </c>
+      <c r="G56" t="s">
+        <v>39</v>
+      </c>
+      <c r="H56">
+        <v>3543</v>
+      </c>
+      <c r="I56">
+        <v>1.3353090000000001</v>
+      </c>
+      <c r="J56">
+        <v>48.834862389999998</v>
+      </c>
+      <c r="K56" t="s">
+        <v>34</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>5323</v>
+      </c>
+      <c r="N56" t="s">
+        <v>85</v>
+      </c>
+      <c r="O56">
+        <v>4731</v>
+      </c>
+      <c r="P56">
+        <v>1125.1321069999999</v>
+      </c>
+      <c r="Q56">
+        <v>109</v>
+      </c>
+      <c r="S56">
+        <v>48.834862000000001</v>
+      </c>
+      <c r="T56">
+        <v>2.3039529999999999</v>
+      </c>
+      <c r="U56">
+        <v>130</v>
+      </c>
+      <c r="V56">
+        <v>2.747833</v>
+      </c>
+      <c r="W56">
+        <v>40.946154</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" t="s">
+        <v>84</v>
+      </c>
+      <c r="D57" t="s">
+        <v>83</v>
+      </c>
+      <c r="E57" t="s">
+        <v>29</v>
+      </c>
+      <c r="F57">
+        <v>180</v>
+      </c>
+      <c r="G57" t="s">
+        <v>49</v>
+      </c>
+      <c r="H57">
+        <v>3324</v>
+      </c>
+      <c r="I57">
+        <v>1.4750300000000001</v>
+      </c>
+      <c r="J57">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="K57" t="s">
+        <v>34</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>6354</v>
+      </c>
+      <c r="N57" t="s">
+        <v>81</v>
+      </c>
+      <c r="O57">
+        <v>4903</v>
+      </c>
+      <c r="P57">
+        <v>1295.9412600000001</v>
+      </c>
+      <c r="Q57">
+        <v>191</v>
+      </c>
+      <c r="S57">
+        <v>33.267015999999998</v>
+      </c>
+      <c r="T57">
+        <v>3.8955739999999999</v>
+      </c>
+      <c r="U57">
+        <v>232</v>
+      </c>
+      <c r="V57">
+        <v>4.7317970000000003</v>
+      </c>
+      <c r="W57">
+        <v>27.387930999999998</v>
+      </c>
+      <c r="X57">
+        <v>180</v>
+      </c>
+      <c r="Y57">
+        <v>35.299999999999997</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D58" t="s">
+        <v>28</v>
+      </c>
+      <c r="E58" t="s">
+        <v>29</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="K58" t="s">
+        <v>34</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58" t="s">
+        <v>81</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" t="s">
+        <v>80</v>
+      </c>
+      <c r="D59" t="s">
+        <v>38</v>
+      </c>
+      <c r="E59" t="s">
+        <v>29</v>
+      </c>
+      <c r="F59">
+        <v>204</v>
+      </c>
+      <c r="G59" t="s">
+        <v>49</v>
+      </c>
+      <c r="H59">
+        <v>3954</v>
+      </c>
+      <c r="I59">
+        <v>1.925392</v>
+      </c>
+      <c r="J59">
+        <v>28.877450979999999</v>
+      </c>
+      <c r="K59" t="s">
+        <v>34</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>5891</v>
+      </c>
+      <c r="N59" t="s">
+        <v>76</v>
+      </c>
+      <c r="O59">
+        <v>7613</v>
+      </c>
+      <c r="P59">
+        <v>773.80795999999998</v>
+      </c>
+      <c r="Q59">
+        <v>201</v>
+      </c>
+      <c r="S59">
+        <v>29.308458000000002</v>
+      </c>
+      <c r="T59">
+        <v>2.6402209999999999</v>
+      </c>
+      <c r="U59">
+        <v>217</v>
+      </c>
+      <c r="V59">
+        <v>2.8503880000000001</v>
+      </c>
+      <c r="W59">
+        <v>27.147465</v>
+      </c>
+      <c r="X59">
+        <v>204</v>
+      </c>
+      <c r="Y59">
+        <v>28.877451000000001</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>